--- a/public/RMS-FORMv2.xlsx
+++ b/public/RMS-FORMv2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\RMS\rms-admin-reactjs\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C97F759-77E7-41C7-A010-F3506D095FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA983476-B865-480B-A292-AB92DAFB2722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{2516D39E-AF4F-42BA-81E3-AEC62EE68D27}"/>
   </bookViews>
@@ -4872,7 +4872,7 @@
       <c r="U65" s="85"/>
       <c r="V65" s="85"/>
     </row>
-    <row r="66" spans="1:22" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:22" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="107"/>
       <c r="B66" s="107"/>
       <c r="C66" s="107"/>
@@ -7007,7 +7007,7 @@
       <c r="U148" s="58"/>
       <c r="V148" s="59"/>
     </row>
-    <row r="149" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="57"/>
       <c r="B149" s="58"/>
       <c r="C149" s="58"/>
@@ -7105,7 +7105,7 @@
       <c r="U152" s="54"/>
       <c r="V152" s="55"/>
     </row>
-    <row r="153" spans="1:22" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:22" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="36" t="s">
         <v>144</v>
       </c>
